--- a/artfynd/A 66998-2021 artfynd.xlsx
+++ b/artfynd/A 66998-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66998-2021 artfynd.xlsx
+++ b/artfynd/A 66998-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17225951</v>
+        <v>17225941</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550948.5958458979</v>
+        <v>551057</v>
       </c>
       <c r="R2" t="n">
-        <v>7241415.296994488</v>
+        <v>7241557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,37 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17225967</v>
+        <v>17225955</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551011.4531476158</v>
+        <v>550934</v>
       </c>
       <c r="R3" t="n">
-        <v>7241826.140635618</v>
+        <v>7241485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,37 +913,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17225947</v>
+        <v>17226000</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550979.8170151031</v>
+        <v>551349</v>
       </c>
       <c r="R4" t="n">
-        <v>7241475.693246546</v>
+        <v>7242297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17226002</v>
+        <v>17225995</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,34 +1043,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551501.2682436955</v>
+        <v>551283</v>
       </c>
       <c r="R5" t="n">
-        <v>7242209.226070885</v>
+        <v>7242305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,21 +1102,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1176,12 +1118,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1189,7 +1136,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,19 +1158,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17225979</v>
+        <v>17225962</v>
       </c>
       <c r="B6" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1251,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551187.4463633044</v>
+        <v>550911</v>
       </c>
       <c r="R6" t="n">
-        <v>7242138.465168206</v>
+        <v>7241724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,19 +1226,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,15 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17225978</v>
+        <v>17225979</v>
       </c>
       <c r="B7" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,21 +1288,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1385,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551179.6632263736</v>
+        <v>551187</v>
       </c>
       <c r="R7" t="n">
-        <v>7242128.286360584</v>
+        <v>7242138</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,19 +1345,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,15 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17225953</v>
+        <v>17225926</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1519,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550813.754724346</v>
+        <v>551264</v>
       </c>
       <c r="R8" t="n">
-        <v>7241433.892855129</v>
+        <v>7241759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,19 +1464,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,15 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17226012</v>
+        <v>17225983</v>
       </c>
       <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,21 +1526,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1653,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551430.8356707711</v>
+        <v>551224</v>
       </c>
       <c r="R9" t="n">
-        <v>7242571.1963949</v>
+        <v>7242039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,21 +1583,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1721,11 +1608,11 @@
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>2 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1747,15 +1634,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17226013</v>
+        <v>17225920</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,34 +1645,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551458.0560575112</v>
+        <v>551211</v>
       </c>
       <c r="R10" t="n">
-        <v>7242571.672730329</v>
+        <v>7241849</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1689,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1817,22 +1699,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,15 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17225954</v>
+        <v>17225937</v>
       </c>
       <c r="B11" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550813.754724346</v>
+        <v>551105</v>
       </c>
       <c r="R11" t="n">
-        <v>7241433.892855129</v>
+        <v>7241537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,19 +1821,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2015,15 +1872,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17225945</v>
+        <v>17225947</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2031,21 +1883,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2055,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550985.5787066368</v>
+        <v>550980</v>
       </c>
       <c r="R12" t="n">
-        <v>7241505.929579234</v>
+        <v>7241476</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2088,19 +1940,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2149,15 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17225966</v>
+        <v>17225952</v>
       </c>
       <c r="B13" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2165,21 +2002,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2189,10 +2026,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551001.8643984845</v>
+        <v>550828</v>
       </c>
       <c r="R13" t="n">
-        <v>7241799.189272274</v>
+        <v>7241434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2222,19 +2059,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2283,37 +2110,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17225975</v>
+        <v>17225953</v>
       </c>
       <c r="B14" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2323,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551127.7594550452</v>
+        <v>550814</v>
       </c>
       <c r="R14" t="n">
-        <v>7242101.437981707</v>
+        <v>7241434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2356,19 +2178,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2417,15 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17225984</v>
+        <v>17225959</v>
       </c>
       <c r="B15" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2433,21 +2240,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2457,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551551.244162698</v>
+        <v>550736</v>
       </c>
       <c r="R15" t="n">
-        <v>7242082.886385445</v>
+        <v>7241603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2487,22 +2294,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2554,12 +2351,7 @@
         <v>17225963</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2576,12 +2368,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2591,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550986.2750427179</v>
+        <v>550986</v>
       </c>
       <c r="R16" t="n">
-        <v>7241755.811254553</v>
+        <v>7241756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2624,19 +2416,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2685,15 +2467,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17225977</v>
+        <v>17225968</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2710,12 +2487,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2725,10 +2502,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551137.779405497</v>
+        <v>551031</v>
       </c>
       <c r="R17" t="n">
-        <v>7242127.557630342</v>
+        <v>7241876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2758,19 +2535,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2819,37 +2586,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17226000</v>
+        <v>17225970</v>
       </c>
       <c r="B18" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2859,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551349.3239575272</v>
+        <v>550979</v>
       </c>
       <c r="R18" t="n">
-        <v>7242297.373486195</v>
+        <v>7241946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,22 +2651,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2953,15 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17225983</v>
+        <v>17225974</v>
       </c>
       <c r="B19" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2969,21 +2716,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2993,10 +2740,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551223.5400468378</v>
+        <v>551179</v>
       </c>
       <c r="R19" t="n">
-        <v>7242038.658926133</v>
+        <v>7242038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3023,22 +2770,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3061,11 +2798,11 @@
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3087,15 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17225949</v>
+        <v>17225977</v>
       </c>
       <c r="B20" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3103,21 +2835,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3127,10 +2859,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551015.0661088801</v>
+        <v>551138</v>
       </c>
       <c r="R20" t="n">
-        <v>7241376.265917607</v>
+        <v>7242128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3160,19 +2892,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3221,15 +2943,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17225959</v>
+        <v>17225989</v>
       </c>
       <c r="B21" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3246,12 +2963,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3261,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550736.2460101334</v>
+        <v>551285</v>
       </c>
       <c r="R21" t="n">
-        <v>7241602.907385275</v>
+        <v>7242217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3291,22 +3008,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3355,15 +3062,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17225962</v>
+        <v>17226001</v>
       </c>
       <c r="B22" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3371,21 +3073,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3395,10 +3097,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550910.984492773</v>
+        <v>551349</v>
       </c>
       <c r="R22" t="n">
-        <v>7241723.954447974</v>
+        <v>7242297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3425,22 +3127,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3489,50 +3181,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17226008</v>
+        <v>17225924</v>
       </c>
       <c r="B23" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551515.1184295503</v>
+        <v>551234</v>
       </c>
       <c r="R23" t="n">
-        <v>7242542.546326263</v>
+        <v>7241829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3549,7 +3236,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3559,22 +3246,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3623,15 +3300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17225989</v>
+        <v>17225925</v>
       </c>
       <c r="B24" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3639,21 +3311,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3663,10 +3335,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>551285.3753147661</v>
+        <v>551255</v>
       </c>
       <c r="R24" t="n">
-        <v>7242216.750891227</v>
+        <v>7241829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3693,22 +3365,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3757,15 +3419,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17225948</v>
+        <v>17225942</v>
       </c>
       <c r="B25" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3773,21 +3430,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3797,10 +3454,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550979.8170151031</v>
+        <v>551005</v>
       </c>
       <c r="R25" t="n">
-        <v>7241475.693246546</v>
+        <v>7241546</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3830,21 +3487,11 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3865,11 +3512,11 @@
         </is>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>2 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3891,37 +3538,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>17225987</v>
+        <v>17225943</v>
       </c>
       <c r="B26" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3931,10 +3573,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>551399.9188027183</v>
+        <v>551005</v>
       </c>
       <c r="R26" t="n">
-        <v>7242111.204641286</v>
+        <v>7241556</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3961,22 +3603,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4025,15 +3657,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17226001</v>
+        <v>17225991</v>
       </c>
       <c r="B27" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4041,21 +3668,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4065,10 +3692,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>551349.3239575272</v>
+        <v>551233</v>
       </c>
       <c r="R27" t="n">
-        <v>7242297.373486195</v>
+        <v>7242211</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4098,21 +3725,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4133,11 +3750,11 @@
         </is>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>2 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4159,15 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17225973</v>
+        <v>17225992</v>
       </c>
       <c r="B28" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4175,21 +3787,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4199,10 +3811,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>551196.1288452789</v>
+        <v>551194</v>
       </c>
       <c r="R28" t="n">
-        <v>7241928.536329259</v>
+        <v>7242216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4229,22 +3841,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4293,37 +3895,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>17225982</v>
+        <v>17225998</v>
       </c>
       <c r="B29" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4333,10 +3930,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>551334.0888910674</v>
+        <v>551302</v>
       </c>
       <c r="R29" t="n">
-        <v>7241850.169598127</v>
+        <v>7242324</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4363,22 +3960,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4427,37 +4014,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17225922</v>
+        <v>17225975</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4467,10 +4049,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>551211.3430690118</v>
+        <v>551128</v>
       </c>
       <c r="R30" t="n">
-        <v>7241848.866474408</v>
+        <v>7242101</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,19 +4082,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4561,37 +4133,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>17225971</v>
+        <v>17225978</v>
       </c>
       <c r="B31" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4601,10 +4168,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>551090.3227459341</v>
+        <v>551180</v>
       </c>
       <c r="R31" t="n">
-        <v>7241917.070603896</v>
+        <v>7242128</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4634,19 +4201,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4695,50 +4252,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17226005</v>
+        <v>17225982</v>
       </c>
       <c r="B32" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551661.9194045354</v>
+        <v>551334</v>
       </c>
       <c r="R32" t="n">
-        <v>7242484.451442922</v>
+        <v>7241850</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4755,7 +4307,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4765,22 +4317,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4829,37 +4371,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17225992</v>
+        <v>17225987</v>
       </c>
       <c r="B33" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4869,10 +4406,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551194.4828516694</v>
+        <v>551400</v>
       </c>
       <c r="R33" t="n">
-        <v>7242215.585359649</v>
+        <v>7242111</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4902,19 +4439,9 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4963,50 +4490,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17226007</v>
+        <v>17225988</v>
       </c>
       <c r="B34" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>551515.1184295503</v>
+        <v>551358</v>
       </c>
       <c r="R34" t="n">
-        <v>7242542.546326263</v>
+        <v>7242141</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5023,7 +4545,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5036,19 +4558,9 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5097,15 +4609,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17225921</v>
+        <v>17225993</v>
       </c>
       <c r="B35" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5113,21 +4620,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>918</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5137,10 +4644,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>551211.3430690118</v>
+        <v>551226</v>
       </c>
       <c r="R35" t="n">
-        <v>7241848.866474408</v>
+        <v>7242269</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5167,22 +4674,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5231,15 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17225952</v>
+        <v>17225957</v>
       </c>
       <c r="B36" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5247,21 +4739,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5271,10 +4763,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550828.4175149592</v>
+        <v>550767</v>
       </c>
       <c r="R36" t="n">
-        <v>7241434.146214709</v>
+        <v>7241553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5304,19 +4796,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5365,37 +4847,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17225965</v>
+        <v>17225961</v>
       </c>
       <c r="B37" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5405,10 +4882,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>551001.8643984845</v>
+        <v>550884</v>
       </c>
       <c r="R37" t="n">
-        <v>7241799.189272274</v>
+        <v>7241700</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5438,19 +4915,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5499,15 +4966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17225994</v>
+        <v>17225971</v>
       </c>
       <c r="B38" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5515,21 +4977,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5539,10 +5001,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>551207.8049098697</v>
+        <v>551090</v>
       </c>
       <c r="R38" t="n">
-        <v>7242268.542871124</v>
+        <v>7241917</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5569,22 +5031,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5633,15 +5085,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17225976</v>
+        <v>17225980</v>
       </c>
       <c r="B39" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5649,21 +5096,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5673,10 +5120,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>551145.9119776414</v>
+        <v>551279</v>
       </c>
       <c r="R39" t="n">
-        <v>7242117.655725579</v>
+        <v>7241997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5706,19 +5153,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5767,15 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17225943</v>
+        <v>17225922</v>
       </c>
       <c r="B40" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5783,21 +5215,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5807,10 +5239,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551004.8236545296</v>
+        <v>551211</v>
       </c>
       <c r="R40" t="n">
-        <v>7241556.071462902</v>
+        <v>7241849</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5840,19 +5272,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5901,15 +5323,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17226009</v>
+        <v>17225938</v>
       </c>
       <c r="B41" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5917,34 +5334,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551483.9529507448</v>
+        <v>551105</v>
       </c>
       <c r="R41" t="n">
-        <v>7242552.042332351</v>
+        <v>7241537</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5961,7 +5378,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5971,22 +5388,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6035,15 +5442,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>17225961</v>
+        <v>17225951</v>
       </c>
       <c r="B42" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6051,21 +5453,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6075,10 +5477,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550884.1689227117</v>
+        <v>550949</v>
       </c>
       <c r="R42" t="n">
-        <v>7241699.634134089</v>
+        <v>7241415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6108,19 +5510,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6169,15 +5561,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17225968</v>
+        <v>17225976</v>
       </c>
       <c r="B43" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6185,21 +5572,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6209,10 +5596,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551030.6954486071</v>
+        <v>551146</v>
       </c>
       <c r="R43" t="n">
-        <v>7241876.277297182</v>
+        <v>7242118</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6242,19 +5629,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6303,37 +5680,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17225974</v>
+        <v>17225940</v>
       </c>
       <c r="B44" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6343,10 +5715,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551178.7157080987</v>
+        <v>551117</v>
       </c>
       <c r="R44" t="n">
-        <v>7242038.296901991</v>
+        <v>7241508</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6376,19 +5748,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6437,37 +5799,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17225920</v>
+        <v>17225944</v>
       </c>
       <c r="B45" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6477,10 +5834,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551211.3430690118</v>
+        <v>550975</v>
       </c>
       <c r="R45" t="n">
-        <v>7241848.866474408</v>
+        <v>7241546</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6510,19 +5867,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6571,19 +5918,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17225986</v>
+        <v>17225945</v>
       </c>
       <c r="B46" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -6611,10 +5953,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551481.6746309528</v>
+        <v>550986</v>
       </c>
       <c r="R46" t="n">
-        <v>7242131.884783894</v>
+        <v>7241506</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6641,22 +5983,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6705,37 +6037,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17226004</v>
+        <v>17225948</v>
       </c>
       <c r="B47" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6745,10 +6072,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551595.9454925383</v>
+        <v>550980</v>
       </c>
       <c r="R47" t="n">
-        <v>7242233.482876502</v>
+        <v>7241476</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6775,22 +6102,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6813,11 +6130,11 @@
         </is>
       </c>
       <c r="AN47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>2 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6839,19 +6156,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17225969</v>
+        <v>17225949</v>
       </c>
       <c r="B48" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6879,10 +6191,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551030.6954486071</v>
+        <v>551015</v>
       </c>
       <c r="R48" t="n">
-        <v>7241876.277297182</v>
+        <v>7241376</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6912,19 +6224,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6973,19 +6275,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>17225960</v>
+        <v>17225950</v>
       </c>
       <c r="B49" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -7013,10 +6310,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550843.1549084883</v>
+        <v>551012</v>
       </c>
       <c r="R49" t="n">
-        <v>7241624.006667583</v>
+        <v>7241366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7046,19 +6343,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7107,15 +6394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>17225993</v>
+        <v>17225954</v>
       </c>
       <c r="B50" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7123,21 +6405,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7147,10 +6429,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>551225.8140918525</v>
+        <v>550814</v>
       </c>
       <c r="R50" t="n">
-        <v>7242268.856584115</v>
+        <v>7241434</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7177,22 +6459,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7241,15 +6513,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17225988</v>
+        <v>17225956</v>
       </c>
       <c r="B51" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7257,21 +6524,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7281,10 +6548,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>551357.5086189288</v>
+        <v>550686</v>
       </c>
       <c r="R51" t="n">
-        <v>7242140.593705953</v>
+        <v>7241502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7311,22 +6578,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7375,19 +6632,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>17225950</v>
+        <v>17225958</v>
       </c>
       <c r="B52" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -7415,10 +6667,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>551012.307672236</v>
+        <v>550748</v>
       </c>
       <c r="R52" t="n">
-        <v>7241366.172178016</v>
+        <v>7241590</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7448,19 +6700,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7509,19 +6751,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17225958</v>
+        <v>17225960</v>
       </c>
       <c r="B53" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -7549,10 +6786,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550747.7876938283</v>
+        <v>550843</v>
       </c>
       <c r="R53" t="n">
-        <v>7241589.71305799</v>
+        <v>7241624</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7582,19 +6819,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7643,37 +6870,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>17225957</v>
+        <v>17225964</v>
       </c>
       <c r="B54" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7683,10 +6905,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550767.2744504916</v>
+        <v>550986</v>
       </c>
       <c r="R54" t="n">
-        <v>7241553.217036509</v>
+        <v>7241756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7716,19 +6938,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7777,37 +6989,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>17225925</v>
+        <v>17225966</v>
       </c>
       <c r="B55" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7817,10 +7024,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>551255.2636975766</v>
+        <v>551002</v>
       </c>
       <c r="R55" t="n">
-        <v>7241829.124485917</v>
+        <v>7241799</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7850,19 +7057,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7911,37 +7108,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>17225924</v>
+        <v>17225967</v>
       </c>
       <c r="B56" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7951,10 +7143,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>551234.3123661131</v>
+        <v>551011</v>
       </c>
       <c r="R56" t="n">
-        <v>7241829.177903932</v>
+        <v>7241826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7984,19 +7176,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8045,37 +7227,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17225970</v>
+        <v>17225969</v>
       </c>
       <c r="B57" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8085,10 +7262,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550978.793168128</v>
+        <v>551031</v>
       </c>
       <c r="R57" t="n">
-        <v>7241945.685460407</v>
+        <v>7241876</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8118,19 +7295,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8179,15 +7346,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17226006</v>
+        <v>17225972</v>
       </c>
       <c r="B58" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8195,34 +7357,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>551562.2051184293</v>
+        <v>551197</v>
       </c>
       <c r="R58" t="n">
-        <v>7242532.911393671</v>
+        <v>7241903</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8239,7 +7401,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8249,22 +7411,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8313,19 +7465,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>17225956</v>
+        <v>17225973</v>
       </c>
       <c r="B59" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -8353,10 +7500,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550685.6053349646</v>
+        <v>551196</v>
       </c>
       <c r="R59" t="n">
-        <v>7241502.000363247</v>
+        <v>7241929</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8386,19 +7533,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8447,19 +7584,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17226003</v>
+        <v>17225994</v>
       </c>
       <c r="B60" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -8487,10 +7619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>551595.9454925383</v>
+        <v>551208</v>
       </c>
       <c r="R60" t="n">
-        <v>7242233.482876502</v>
+        <v>7242269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8520,19 +7652,9 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8581,15 +7703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>17225964</v>
+        <v>17225921</v>
       </c>
       <c r="B61" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8597,21 +7714,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8621,10 +7738,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550986.2750427179</v>
+        <v>551211</v>
       </c>
       <c r="R61" t="n">
-        <v>7241755.811254553</v>
+        <v>7241849</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8654,19 +7771,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8715,15 +7822,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17225972</v>
+        <v>17225936</v>
       </c>
       <c r="B62" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8731,21 +7833,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8755,10 +7857,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>551196.5804518785</v>
+        <v>551105</v>
       </c>
       <c r="R62" t="n">
-        <v>7241902.59701784</v>
+        <v>7241537</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8788,19 +7890,9 @@
           <t>2014-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8849,53 +7941,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>17225955</v>
+        <v>88130181</v>
       </c>
       <c r="B63" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Vaartoe, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550933.9723681866</v>
+        <v>550964</v>
       </c>
       <c r="R63" t="n">
-        <v>7241485.363041621</v>
+        <v>7241113</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8919,22 +8006,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8945,53 +8022,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17225998</v>
+        <v>17225981</v>
       </c>
       <c r="B64" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8999,34 +8049,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>551301.9423144056</v>
+        <v>551314</v>
       </c>
       <c r="R64" t="n">
-        <v>7242323.745433983</v>
+        <v>7241895</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9053,22 +8105,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9082,12 +8124,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN64" t="n">
@@ -9095,7 +8142,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9117,15 +8164,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17225944</v>
+        <v>17225990</v>
       </c>
       <c r="B65" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9133,34 +8175,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550975.2471651346</v>
+        <v>551277</v>
       </c>
       <c r="R65" t="n">
-        <v>7241545.931956407</v>
+        <v>7242194</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9187,22 +8231,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9222,6 +8256,11 @@
       <c r="AK65" t="inlineStr">
         <is>
           <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN65" t="n">
@@ -9229,7 +8268,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9251,15 +8290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>17225991</v>
+        <v>17225997</v>
       </c>
       <c r="B66" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9267,34 +8301,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>551232.690751503</v>
+        <v>551276</v>
       </c>
       <c r="R66" t="n">
-        <v>7242210.810880678</v>
+        <v>7242297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9324,21 +8360,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9358,12 +8384,17 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AN66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>2 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9385,15 +8416,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>17225980</v>
+        <v>17225999</v>
       </c>
       <c r="B67" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9401,21 +8427,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9425,10 +8451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>551279.1609785934</v>
+        <v>551331</v>
       </c>
       <c r="R67" t="n">
-        <v>7241996.524045323</v>
+        <v>7242300</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9455,22 +8481,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9484,12 +8500,12 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AN67" t="n">
@@ -9497,7 +8513,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Betula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9519,37 +8535,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17225999</v>
+        <v>17225965</v>
       </c>
       <c r="B68" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1467</v>
+        <v>1506</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9559,10 +8570,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>551331.2638237681</v>
+        <v>551002</v>
       </c>
       <c r="R68" t="n">
-        <v>7242299.987267933</v>
+        <v>7241799</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9589,22 +8600,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9618,12 +8619,12 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN68" t="n">
@@ -9631,7 +8632,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>1 substratenheter # Betula</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9653,15 +8654,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>17225942</v>
+        <v>88130183</v>
       </c>
       <c r="B69" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78770</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9669,37 +8665,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>1561</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Urnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tholurna dissimilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) Norman</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Vaartoe, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>551004.9978116446</v>
+        <v>550990</v>
       </c>
       <c r="R69" t="n">
-        <v>7241546.029199744</v>
+        <v>7241082</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9723,22 +8719,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9749,93 +8735,67 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17225981</v>
+        <v>88130182</v>
       </c>
       <c r="B70" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Vaartoe, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>551313.6131555244</v>
+        <v>550966</v>
       </c>
       <c r="R70" t="n">
-        <v>7241895.01126864</v>
+        <v>7241117</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9859,22 +8819,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9883,97 +8833,67 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AN70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>17225997</v>
+        <v>17225996</v>
       </c>
       <c r="B71" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1467</v>
+        <v>6443</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>551275.6053552962</v>
+        <v>551276</v>
       </c>
       <c r="R71" t="n">
-        <v>7242296.505372751</v>
+        <v>7242297</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10003,19 +8923,14 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Artbestämd av Anders Nordin</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10024,6 +8939,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -10035,11 +8951,6 @@
       <c r="AK71" t="inlineStr">
         <is>
           <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN71" t="n">
@@ -10047,7 +8958,12 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # Picea abies</t>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10069,15 +8985,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>17225995</v>
+        <v>17226004</v>
       </c>
       <c r="B72" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10085,36 +8996,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>551283.4241909861</v>
+        <v>551596</v>
       </c>
       <c r="R72" t="n">
-        <v>7242304.592266508</v>
+        <v>7242233</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10144,21 +9053,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10170,17 +9069,12 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN72" t="n">
@@ -10188,7 +9082,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10210,15 +9104,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>17225990</v>
+        <v>17226009</v>
       </c>
       <c r="B73" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10226,36 +9115,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>551276.5478131141</v>
+        <v>551484</v>
       </c>
       <c r="R73" t="n">
-        <v>7242194.418438589</v>
+        <v>7242552</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10272,7 +9159,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Åsele lappmark</t>
+          <t>Lycksele lappmark</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -10285,21 +9172,11 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -10317,11 +9194,6 @@
       <c r="AK73" t="inlineStr">
         <is>
           <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN73" t="n">
@@ -10329,7 +9201,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # Picea abies</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10351,15 +9223,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>17225985</v>
+        <v>17226014</v>
       </c>
       <c r="B74" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10367,36 +9234,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>551547.8868699662</v>
+        <v>551778</v>
       </c>
       <c r="R74" t="n">
-        <v>7242107.099325672</v>
+        <v>7242695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10413,7 +9281,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Åsele lappmark</t>
+          <t>Lycksele lappmark</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10426,43 +9294,29 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN74" t="n">
@@ -10470,7 +9324,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10492,53 +9346,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17225996</v>
+        <v>17226006</v>
       </c>
       <c r="B75" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6443</v>
+        <v>918</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>551275.6053552962</v>
+        <v>551562</v>
       </c>
       <c r="R75" t="n">
-        <v>7242296.505372751</v>
+        <v>7242533</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10555,7 +9401,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Åsele lappmark</t>
+          <t>Lycksele lappmark</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -10568,33 +9414,17 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Artbestämd av Anders Nordin</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10614,11 +9444,6 @@
       <c r="AO75" t="inlineStr">
         <is>
           <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10640,15 +9465,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88130182</v>
+        <v>17226012</v>
       </c>
       <c r="B76" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10656,40 +9476,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vaartoe, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550965.914686559</v>
+        <v>551431</v>
       </c>
       <c r="R76" t="n">
-        <v>7241117.139771971</v>
+        <v>7242571</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10713,22 +9530,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10737,34 +9544,50 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>88130183</v>
+        <v>17226005</v>
       </c>
       <c r="B77" t="n">
-        <v>76968</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10772,37 +9595,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1561</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Urnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tholurna dissimilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Norman) Norman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vaartoe, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550989.9942841808</v>
+        <v>551662</v>
       </c>
       <c r="R77" t="n">
-        <v>7241081.97459418</v>
+        <v>7242484</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10816,7 +9639,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Åsele lappmark</t>
+          <t>Lycksele lappmark</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -10826,22 +9649,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10852,69 +9665,86 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>88130181</v>
+        <v>17225984</v>
       </c>
       <c r="B78" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vaartoe, Ås lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550963.8922808679</v>
+        <v>551551</v>
       </c>
       <c r="R78" t="n">
-        <v>7241112.918581163</v>
+        <v>7242083</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10938,22 +9768,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10964,69 +9784,83 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>17226014</v>
+        <v>17225986</v>
       </c>
       <c r="B79" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>551778.0237040352</v>
+        <v>551482</v>
       </c>
       <c r="R79" t="n">
-        <v>7242694.862274975</v>
+        <v>7242132</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11043,7 +9877,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Lycksele lappmark</t>
+          <t>Åsele lappmark</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -11056,28 +9890,17 @@
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2014-10-04</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -11111,6 +9934,727 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>17226002</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>551501</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7242209</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>17226003</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>551596</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7242233</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>17226007</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>551515</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7242543</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>17226010</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>551458</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7242572</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>17226008</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>551515</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7242543</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>17225985</v>
+      </c>
+      <c r="B85" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sörliden-Erik-Nilshobben, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>551548</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7242107</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Standing dead tree/snags # Betula</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
